--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E468"/>
+  <dimension ref="A1:E471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4991,7 +4991,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TC_FORM_009</t>
+          <t>TC_FORM_008</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 9</t>
+          <t>Verify Forms scenario 8</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5018,7 +5018,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TC_FORM_010</t>
+          <t>TC_FORM_009</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 10</t>
+          <t>Verify Forms scenario 9</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5045,7 +5045,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TC_FORM_011</t>
+          <t>TC_FORM_010</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 11</t>
+          <t>Verify Forms scenario 10</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5072,7 +5072,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TC_FORM_012</t>
+          <t>TC_FORM_011</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 12</t>
+          <t>Verify Forms scenario 11</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5099,7 +5099,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TC_FORM_013</t>
+          <t>TC_FORM_012</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 13</t>
+          <t>Verify Forms scenario 12</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5126,7 +5126,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TC_FORM_014</t>
+          <t>TC_FORM_013</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 14</t>
+          <t>Verify Forms scenario 13</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5153,7 +5153,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TC_FORM_015</t>
+          <t>TC_FORM_014</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 15</t>
+          <t>Verify Forms scenario 14</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5180,7 +5180,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TC_FORM_016</t>
+          <t>TC_FORM_015</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 16</t>
+          <t>Verify Forms scenario 15</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5200,14 +5200,14 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TC_FORM_017</t>
+          <t>TC_FORM_016</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 17</t>
+          <t>Verify Forms scenario 16</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5234,7 +5234,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TC_FORM_018</t>
+          <t>TC_FORM_017</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 18</t>
+          <t>Verify Forms scenario 17</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5261,7 +5261,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TC_FORM_019</t>
+          <t>TC_FORM_018</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 19</t>
+          <t>Verify Forms scenario 18</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5288,7 +5288,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TC_FORM_020</t>
+          <t>TC_FORM_019</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 20</t>
+          <t>Verify Forms scenario 19</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5315,7 +5315,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TC_FORM_021</t>
+          <t>TC_FORM_020</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 21</t>
+          <t>Verify Forms scenario 20</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5342,7 +5342,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TC_FORM_022</t>
+          <t>TC_FORM_021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 22</t>
+          <t>Verify Forms scenario 21</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5369,7 +5369,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TC_FORM_023</t>
+          <t>TC_FORM_022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 23</t>
+          <t>Verify Forms scenario 22</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TC_FORM_024</t>
+          <t>TC_FORM_023</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 24</t>
+          <t>Verify Forms scenario 23</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5423,7 +5423,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TC_FORM_025</t>
+          <t>TC_FORM_024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 25</t>
+          <t>Verify Forms scenario 24</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TC_FORM_026</t>
+          <t>TC_FORM_025</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5460,7 +5460,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 26</t>
+          <t>Verify Forms scenario 25</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5477,7 +5477,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TC_FORM_027</t>
+          <t>TC_FORM_026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 27</t>
+          <t>Verify Forms scenario 26</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5504,7 +5504,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TC_FORM_028</t>
+          <t>TC_FORM_027</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 28</t>
+          <t>Verify Forms scenario 27</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5531,7 +5531,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TC_FORM_029</t>
+          <t>TC_FORM_028</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 29</t>
+          <t>Verify Forms scenario 28</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5558,7 +5558,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TC_FORM_030</t>
+          <t>TC_FORM_029</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 30</t>
+          <t>Verify Forms scenario 29</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5585,7 +5585,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TC_FORM_031</t>
+          <t>TC_FORM_030</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 31</t>
+          <t>Verify Forms scenario 30</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5612,7 +5612,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TC_FORM_032</t>
+          <t>TC_FORM_031</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 32</t>
+          <t>Verify Forms scenario 31</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5639,7 +5639,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TC_FORM_033</t>
+          <t>TC_FORM_032</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 33</t>
+          <t>Verify Forms scenario 32</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5666,7 +5666,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TC_FORM_034</t>
+          <t>TC_FORM_033</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 34</t>
+          <t>Verify Forms scenario 33</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5693,7 +5693,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TC_FORM_035</t>
+          <t>TC_FORM_034</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 35</t>
+          <t>Verify Forms scenario 34</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5720,7 +5720,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TC_FORM_036</t>
+          <t>TC_FORM_035</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 36</t>
+          <t>Verify Forms scenario 35</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5747,7 +5747,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TC_FORM_037</t>
+          <t>TC_FORM_036</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 37</t>
+          <t>Verify Forms scenario 36</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5774,7 +5774,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TC_FORM_038</t>
+          <t>TC_FORM_037</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 38</t>
+          <t>Verify Forms scenario 37</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5801,7 +5801,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TC_FORM_039</t>
+          <t>TC_FORM_038</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 39</t>
+          <t>Verify Forms scenario 38</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TC_FORM_040</t>
+          <t>TC_FORM_039</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 40</t>
+          <t>Verify Forms scenario 39</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5855,7 +5855,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TC_FORM_041</t>
+          <t>TC_FORM_040</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 41</t>
+          <t>Verify Forms scenario 40</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5882,7 +5882,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TC_FORM_042</t>
+          <t>TC_FORM_041</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 42</t>
+          <t>Verify Forms scenario 41</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -5909,7 +5909,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TC_FORM_043</t>
+          <t>TC_FORM_042</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 43</t>
+          <t>Verify Forms scenario 42</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -5936,7 +5936,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TC_FORM_044</t>
+          <t>TC_FORM_043</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 44</t>
+          <t>Verify Forms scenario 43</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -5963,7 +5963,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TC_FORM_045</t>
+          <t>TC_FORM_044</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 45</t>
+          <t>Verify Forms scenario 44</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -5990,7 +5990,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TC_FORM_046</t>
+          <t>TC_FORM_045</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 46</t>
+          <t>Verify Forms scenario 45</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -6017,7 +6017,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TC_FORM_047</t>
+          <t>TC_FORM_046</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 47</t>
+          <t>Verify Forms scenario 46</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TC_FORM_048</t>
+          <t>TC_FORM_047</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 48</t>
+          <t>Verify Forms scenario 47</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -6071,7 +6071,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TC_FORM_049</t>
+          <t>TC_FORM_048</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 49</t>
+          <t>Verify Forms scenario 48</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TC_FORM_050</t>
+          <t>TC_FORM_049</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Verify Forms scenario 50</t>
+          <t>Verify Forms scenario 49</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -6125,17 +6125,17 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TC_CRUD_001</t>
+          <t>TC_FORM_050</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Forms</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 1</t>
+          <t>Verify Forms scenario 50</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -6145,14 +6145,14 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TC_CRUD_002</t>
+          <t>TC_CRUD_001</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 2</t>
+          <t>Verify CRUD Operations scenario 1</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -6179,7 +6179,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TC_CRUD_003</t>
+          <t>TC_CRUD_002</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 3</t>
+          <t>Verify CRUD Operations scenario 2</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TC_CRUD_004</t>
+          <t>TC_CRUD_003</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 4</t>
+          <t>Verify CRUD Operations scenario 3</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -6233,7 +6233,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TC_CRUD_005</t>
+          <t>TC_CRUD_004</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 5</t>
+          <t>Verify CRUD Operations scenario 4</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -6260,7 +6260,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TC_CRUD_006</t>
+          <t>TC_CRUD_005</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 6</t>
+          <t>Verify CRUD Operations scenario 5</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -6280,14 +6280,14 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TC_CRUD_007</t>
+          <t>TC_CRUD_006</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 7</t>
+          <t>Verify CRUD Operations scenario 6</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -6314,7 +6314,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TC_CRUD_008</t>
+          <t>TC_CRUD_007</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 8</t>
+          <t>Verify CRUD Operations scenario 7</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -6341,7 +6341,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TC_CRUD_009</t>
+          <t>TC_CRUD_008</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 9</t>
+          <t>Verify CRUD Operations scenario 8</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -6368,7 +6368,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TC_CRUD_010</t>
+          <t>TC_CRUD_009</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 10</t>
+          <t>Verify CRUD Operations scenario 9</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -6395,7 +6395,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TC_CRUD_011</t>
+          <t>TC_CRUD_010</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 11</t>
+          <t>Verify CRUD Operations scenario 10</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -6422,7 +6422,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TC_CRUD_012</t>
+          <t>TC_CRUD_011</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 12</t>
+          <t>Verify CRUD Operations scenario 11</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -6449,7 +6449,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TC_CRUD_013</t>
+          <t>TC_CRUD_012</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 13</t>
+          <t>Verify CRUD Operations scenario 12</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -6476,7 +6476,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TC_CRUD_014</t>
+          <t>TC_CRUD_013</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 14</t>
+          <t>Verify CRUD Operations scenario 13</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -6503,7 +6503,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>TC_CRUD_015</t>
+          <t>TC_CRUD_014</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 15</t>
+          <t>Verify CRUD Operations scenario 14</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -6530,7 +6530,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>TC_CRUD_016</t>
+          <t>TC_CRUD_015</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 16</t>
+          <t>Verify CRUD Operations scenario 15</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -6550,14 +6550,14 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TC_CRUD_017</t>
+          <t>TC_CRUD_016</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 17</t>
+          <t>Verify CRUD Operations scenario 16</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>TC_CRUD_018</t>
+          <t>TC_CRUD_017</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 18</t>
+          <t>Verify CRUD Operations scenario 17</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -6611,7 +6611,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>TC_CRUD_019</t>
+          <t>TC_CRUD_018</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 19</t>
+          <t>Verify CRUD Operations scenario 18</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -6638,7 +6638,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>TC_CRUD_020</t>
+          <t>TC_CRUD_019</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 20</t>
+          <t>Verify CRUD Operations scenario 19</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -6665,7 +6665,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>TC_CRUD_021</t>
+          <t>TC_CRUD_020</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6675,7 +6675,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 21</t>
+          <t>Verify CRUD Operations scenario 20</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -6692,7 +6692,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TC_CRUD_022</t>
+          <t>TC_CRUD_021</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 22</t>
+          <t>Verify CRUD Operations scenario 21</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -6719,7 +6719,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TC_CRUD_023</t>
+          <t>TC_CRUD_022</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 23</t>
+          <t>Verify CRUD Operations scenario 22</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TC_CRUD_024</t>
+          <t>TC_CRUD_023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 24</t>
+          <t>Verify CRUD Operations scenario 23</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>TC_CRUD_025</t>
+          <t>TC_CRUD_024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 25</t>
+          <t>Verify CRUD Operations scenario 24</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -6800,7 +6800,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TC_CRUD_026</t>
+          <t>TC_CRUD_025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 26</t>
+          <t>Verify CRUD Operations scenario 25</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -6827,7 +6827,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TC_CRUD_027</t>
+          <t>TC_CRUD_026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 27</t>
+          <t>Verify CRUD Operations scenario 26</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -6854,7 +6854,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TC_CRUD_028</t>
+          <t>TC_CRUD_027</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 28</t>
+          <t>Verify CRUD Operations scenario 27</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -6881,7 +6881,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>TC_CRUD_029</t>
+          <t>TC_CRUD_028</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 29</t>
+          <t>Verify CRUD Operations scenario 28</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -6908,7 +6908,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TC_CRUD_030</t>
+          <t>TC_CRUD_029</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 30</t>
+          <t>Verify CRUD Operations scenario 29</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -6935,7 +6935,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TC_CRUD_031</t>
+          <t>TC_CRUD_030</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 31</t>
+          <t>Verify CRUD Operations scenario 30</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>TC_CRUD_032</t>
+          <t>TC_CRUD_031</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 32</t>
+          <t>Verify CRUD Operations scenario 31</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -6989,7 +6989,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TC_CRUD_033</t>
+          <t>TC_CRUD_032</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 33</t>
+          <t>Verify CRUD Operations scenario 32</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -7016,7 +7016,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TC_CRUD_034</t>
+          <t>TC_CRUD_033</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 34</t>
+          <t>Verify CRUD Operations scenario 33</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -7043,7 +7043,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>TC_CRUD_035</t>
+          <t>TC_CRUD_034</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 35</t>
+          <t>Verify CRUD Operations scenario 34</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -7070,7 +7070,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TC_CRUD_036</t>
+          <t>TC_CRUD_035</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 36</t>
+          <t>Verify CRUD Operations scenario 35</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -7097,7 +7097,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>TC_CRUD_037</t>
+          <t>TC_CRUD_036</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 37</t>
+          <t>Verify CRUD Operations scenario 36</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -7124,7 +7124,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>TC_CRUD_038</t>
+          <t>TC_CRUD_037</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 38</t>
+          <t>Verify CRUD Operations scenario 37</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -7151,7 +7151,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>TC_CRUD_039</t>
+          <t>TC_CRUD_038</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 39</t>
+          <t>Verify CRUD Operations scenario 38</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -7178,7 +7178,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TC_CRUD_040</t>
+          <t>TC_CRUD_039</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 40</t>
+          <t>Verify CRUD Operations scenario 39</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -7205,7 +7205,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TC_CRUD_041</t>
+          <t>TC_CRUD_040</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 41</t>
+          <t>Verify CRUD Operations scenario 40</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -7232,7 +7232,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>TC_CRUD_042</t>
+          <t>TC_CRUD_041</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 42</t>
+          <t>Verify CRUD Operations scenario 41</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -7259,7 +7259,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TC_CRUD_043</t>
+          <t>TC_CRUD_042</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 43</t>
+          <t>Verify CRUD Operations scenario 42</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -7286,7 +7286,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>TC_CRUD_044</t>
+          <t>TC_CRUD_043</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 44</t>
+          <t>Verify CRUD Operations scenario 43</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -7313,7 +7313,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>TC_CRUD_045</t>
+          <t>TC_CRUD_044</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 45</t>
+          <t>Verify CRUD Operations scenario 44</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TC_CRUD_046</t>
+          <t>TC_CRUD_045</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 46</t>
+          <t>Verify CRUD Operations scenario 45</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -7367,7 +7367,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TC_CRUD_047</t>
+          <t>TC_CRUD_046</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 47</t>
+          <t>Verify CRUD Operations scenario 46</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -7394,7 +7394,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TC_CRUD_048</t>
+          <t>TC_CRUD_047</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 48</t>
+          <t>Verify CRUD Operations scenario 47</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>TC_CRUD_049</t>
+          <t>TC_CRUD_048</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 49</t>
+          <t>Verify CRUD Operations scenario 48</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -7448,7 +7448,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>TC_CRUD_050</t>
+          <t>TC_CRUD_049</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Verify CRUD Operations scenario 50</t>
+          <t>Verify CRUD Operations scenario 49</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -7475,17 +7475,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>TC_INPUT_001</t>
+          <t>TC_CRUD_050</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>CRUD Operations</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 1</t>
+          <t>Verify CRUD Operations scenario 50</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -7495,14 +7495,14 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>TC_INPUT_002</t>
+          <t>TC_INPUT_001</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 2</t>
+          <t>Verify Input Validation scenario 1</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -7529,7 +7529,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TC_INPUT_003</t>
+          <t>TC_INPUT_002</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 3</t>
+          <t>Verify Input Validation scenario 2</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -7556,7 +7556,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>TC_INPUT_004</t>
+          <t>TC_INPUT_003</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 4</t>
+          <t>Verify Input Validation scenario 3</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -7583,7 +7583,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>TC_INPUT_005</t>
+          <t>TC_INPUT_004</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 5</t>
+          <t>Verify Input Validation scenario 4</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -7610,7 +7610,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>TC_INPUT_006</t>
+          <t>TC_INPUT_005</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 6</t>
+          <t>Verify Input Validation scenario 5</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -7630,14 +7630,14 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>TC_INPUT_007</t>
+          <t>TC_INPUT_006</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 7</t>
+          <t>Verify Input Validation scenario 6</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -7664,7 +7664,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>TC_INPUT_008</t>
+          <t>TC_INPUT_007</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 8</t>
+          <t>Verify Input Validation scenario 7</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>TC_INPUT_009</t>
+          <t>TC_INPUT_008</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 9</t>
+          <t>Verify Input Validation scenario 8</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TC_INPUT_010</t>
+          <t>TC_INPUT_009</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 10</t>
+          <t>Verify Input Validation scenario 9</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -7745,7 +7745,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>TC_INPUT_011</t>
+          <t>TC_INPUT_010</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 11</t>
+          <t>Verify Input Validation scenario 10</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -7772,7 +7772,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TC_INPUT_012</t>
+          <t>TC_INPUT_011</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 12</t>
+          <t>Verify Input Validation scenario 11</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -7799,7 +7799,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>TC_INPUT_013</t>
+          <t>TC_INPUT_012</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 13</t>
+          <t>Verify Input Validation scenario 12</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -7826,7 +7826,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TC_INPUT_014</t>
+          <t>TC_INPUT_013</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 14</t>
+          <t>Verify Input Validation scenario 13</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -7853,7 +7853,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>TC_INPUT_015</t>
+          <t>TC_INPUT_014</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 15</t>
+          <t>Verify Input Validation scenario 14</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -7880,7 +7880,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TC_INPUT_016</t>
+          <t>TC_INPUT_015</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 16</t>
+          <t>Verify Input Validation scenario 15</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TC_INPUT_017</t>
+          <t>TC_INPUT_016</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7917,7 +7917,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 17</t>
+          <t>Verify Input Validation scenario 16</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TC_INPUT_018</t>
+          <t>TC_INPUT_017</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 18</t>
+          <t>Verify Input Validation scenario 17</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -7961,7 +7961,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>TC_INPUT_019</t>
+          <t>TC_INPUT_018</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 19</t>
+          <t>Verify Input Validation scenario 18</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -7988,7 +7988,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>TC_INPUT_020</t>
+          <t>TC_INPUT_019</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 20</t>
+          <t>Verify Input Validation scenario 19</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -8015,7 +8015,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TC_INPUT_021</t>
+          <t>TC_INPUT_020</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -8025,7 +8025,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 21</t>
+          <t>Verify Input Validation scenario 20</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -8042,7 +8042,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>TC_INPUT_022</t>
+          <t>TC_INPUT_021</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 22</t>
+          <t>Verify Input Validation scenario 21</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -8069,7 +8069,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TC_INPUT_023</t>
+          <t>TC_INPUT_022</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 23</t>
+          <t>Verify Input Validation scenario 22</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>TC_INPUT_024</t>
+          <t>TC_INPUT_023</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 24</t>
+          <t>Verify Input Validation scenario 23</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TC_INPUT_025</t>
+          <t>TC_INPUT_024</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 25</t>
+          <t>Verify Input Validation scenario 24</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -8150,7 +8150,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>TC_INPUT_026</t>
+          <t>TC_INPUT_025</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 26</t>
+          <t>Verify Input Validation scenario 25</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -8177,7 +8177,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TC_INPUT_027</t>
+          <t>TC_INPUT_026</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 27</t>
+          <t>Verify Input Validation scenario 26</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8204,7 +8204,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>TC_INPUT_028</t>
+          <t>TC_INPUT_027</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 28</t>
+          <t>Verify Input Validation scenario 27</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8231,7 +8231,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>TC_INPUT_029</t>
+          <t>TC_INPUT_028</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 29</t>
+          <t>Verify Input Validation scenario 28</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8258,7 +8258,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TC_INPUT_030</t>
+          <t>TC_INPUT_029</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 30</t>
+          <t>Verify Input Validation scenario 29</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8285,7 +8285,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>TC_INPUT_031</t>
+          <t>TC_INPUT_030</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 31</t>
+          <t>Verify Input Validation scenario 30</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8312,7 +8312,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TC_INPUT_032</t>
+          <t>TC_INPUT_031</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 32</t>
+          <t>Verify Input Validation scenario 31</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -8339,7 +8339,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TC_INPUT_033</t>
+          <t>TC_INPUT_032</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8349,7 +8349,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 33</t>
+          <t>Verify Input Validation scenario 32</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -8366,7 +8366,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>TC_INPUT_034</t>
+          <t>TC_INPUT_033</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 34</t>
+          <t>Verify Input Validation scenario 33</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>TC_INPUT_035</t>
+          <t>TC_INPUT_034</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 35</t>
+          <t>Verify Input Validation scenario 34</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -8420,7 +8420,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>TC_INPUT_036</t>
+          <t>TC_INPUT_035</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 36</t>
+          <t>Verify Input Validation scenario 35</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -8447,7 +8447,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TC_INPUT_037</t>
+          <t>TC_INPUT_036</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 37</t>
+          <t>Verify Input Validation scenario 36</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TC_INPUT_038</t>
+          <t>TC_INPUT_037</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 38</t>
+          <t>Verify Input Validation scenario 37</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -8501,7 +8501,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TC_INPUT_039</t>
+          <t>TC_INPUT_038</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 39</t>
+          <t>Verify Input Validation scenario 38</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -8528,7 +8528,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>TC_INPUT_040</t>
+          <t>TC_INPUT_039</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Verify Input Validation scenario 40</t>
+          <t>Verify Input Validation scenario 39</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -8555,17 +8555,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>TC_ERR_001</t>
+          <t>TC_INPUT_040</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 1</t>
+          <t>Verify Input Validation scenario 40</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -8575,14 +8575,14 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>TC_ERR_002</t>
+          <t>TC_ERR_001</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 2</t>
+          <t>Verify Error Handling scenario 1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -8609,7 +8609,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>TC_ERR_003</t>
+          <t>TC_ERR_002</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 3</t>
+          <t>Verify Error Handling scenario 2</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -8636,7 +8636,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>TC_ERR_004</t>
+          <t>TC_ERR_003</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 4</t>
+          <t>Verify Error Handling scenario 3</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -8663,7 +8663,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>TC_ERR_005</t>
+          <t>TC_ERR_004</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 5</t>
+          <t>Verify Error Handling scenario 4</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -8690,7 +8690,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>TC_ERR_006</t>
+          <t>TC_ERR_005</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8700,7 +8700,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 6</t>
+          <t>Verify Error Handling scenario 5</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -8710,14 +8710,14 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>TC_ERR_007</t>
+          <t>TC_ERR_006</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 7</t>
+          <t>Verify Error Handling scenario 6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -8744,7 +8744,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>TC_ERR_008</t>
+          <t>TC_ERR_007</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 8</t>
+          <t>Verify Error Handling scenario 7</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -8771,7 +8771,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>TC_ERR_009</t>
+          <t>TC_ERR_008</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 9</t>
+          <t>Verify Error Handling scenario 8</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -8798,7 +8798,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>TC_ERR_010</t>
+          <t>TC_ERR_009</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 10</t>
+          <t>Verify Error Handling scenario 9</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TC_ERR_011</t>
+          <t>TC_ERR_010</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 11</t>
+          <t>Verify Error Handling scenario 10</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TC_ERR_012</t>
+          <t>TC_ERR_011</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 12</t>
+          <t>Verify Error Handling scenario 11</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -8879,7 +8879,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>TC_ERR_013</t>
+          <t>TC_ERR_012</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 13</t>
+          <t>Verify Error Handling scenario 12</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -8906,7 +8906,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>TC_ERR_015</t>
+          <t>TC_ERR_013</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 15</t>
+          <t>Verify Error Handling scenario 13</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -8933,7 +8933,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>TC_ERR_016</t>
+          <t>TC_ERR_014</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 16</t>
+          <t>Verify Error Handling scenario 14</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -8953,14 +8953,14 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>TC_ERR_017</t>
+          <t>TC_ERR_015</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 17</t>
+          <t>Verify Error Handling scenario 15</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -8980,14 +8980,14 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>TC_ERR_018</t>
+          <t>TC_ERR_016</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 18</t>
+          <t>Verify Error Handling scenario 16</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -9014,7 +9014,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>TC_ERR_019</t>
+          <t>TC_ERR_017</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 19</t>
+          <t>Verify Error Handling scenario 17</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -9041,7 +9041,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>TC_ERR_020</t>
+          <t>TC_ERR_018</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Verify Error Handling scenario 20</t>
+          <t>Verify Error Handling scenario 18</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -9068,17 +9068,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>TC_SESS_001</t>
+          <t>TC_ERR_019</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 1</t>
+          <t>Verify Error Handling scenario 19</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -9088,24 +9088,24 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>TC_SESS_002</t>
+          <t>TC_ERR_020</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Error Handling</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 2</t>
+          <t>Verify Error Handling scenario 20</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -9115,14 +9115,14 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>TC_SESS_003</t>
+          <t>TC_SESS_001</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -9132,7 +9132,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 3</t>
+          <t>Verify Session Management scenario 1</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9149,7 +9149,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>TC_SESS_004</t>
+          <t>TC_SESS_002</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -9159,7 +9159,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 4</t>
+          <t>Verify Session Management scenario 2</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -9176,7 +9176,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>TC_SESS_005</t>
+          <t>TC_SESS_003</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 5</t>
+          <t>Verify Session Management scenario 3</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -9203,7 +9203,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>TC_SESS_006</t>
+          <t>TC_SESS_004</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 6</t>
+          <t>Verify Session Management scenario 4</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -9223,14 +9223,14 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>TC_SESS_007</t>
+          <t>TC_SESS_005</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 7</t>
+          <t>Verify Session Management scenario 5</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -9250,14 +9250,14 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>TC_SESS_008</t>
+          <t>TC_SESS_006</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 8</t>
+          <t>Verify Session Management scenario 6</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -9284,7 +9284,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>TC_SESS_009</t>
+          <t>TC_SESS_007</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 9</t>
+          <t>Verify Session Management scenario 7</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -9311,7 +9311,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>TC_SESS_010</t>
+          <t>TC_SESS_008</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 10</t>
+          <t>Verify Session Management scenario 8</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -9338,7 +9338,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>TC_SESS_011</t>
+          <t>TC_SESS_009</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 11</t>
+          <t>Verify Session Management scenario 9</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -9365,7 +9365,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>TC_SESS_012</t>
+          <t>TC_SESS_010</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 12</t>
+          <t>Verify Session Management scenario 10</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -9392,7 +9392,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>TC_SESS_013</t>
+          <t>TC_SESS_011</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 13</t>
+          <t>Verify Session Management scenario 11</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -9419,7 +9419,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>TC_SESS_014</t>
+          <t>TC_SESS_012</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 14</t>
+          <t>Verify Session Management scenario 12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>TC_SESS_015</t>
+          <t>TC_SESS_013</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 15</t>
+          <t>Verify Session Management scenario 13</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -9473,7 +9473,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>TC_SESS_016</t>
+          <t>TC_SESS_014</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 16</t>
+          <t>Verify Session Management scenario 14</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -9493,14 +9493,14 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>TC_SESS_017</t>
+          <t>TC_SESS_015</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 17</t>
+          <t>Verify Session Management scenario 15</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -9520,14 +9520,14 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>TC_SESS_018</t>
+          <t>TC_SESS_016</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -9537,7 +9537,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 18</t>
+          <t>Verify Session Management scenario 16</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -9554,7 +9554,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>TC_SESS_019</t>
+          <t>TC_SESS_017</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 19</t>
+          <t>Verify Session Management scenario 17</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -9581,7 +9581,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>TC_SESS_020</t>
+          <t>TC_SESS_018</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Verify Session Management scenario 20</t>
+          <t>Verify Session Management scenario 18</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -9608,17 +9608,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>TC_FILE_001</t>
+          <t>TC_SESS_019</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 1</t>
+          <t>Verify Session Management scenario 19</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -9628,24 +9628,24 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>TC_FILE_003</t>
+          <t>TC_SESS_020</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 3</t>
+          <t>Verify Session Management scenario 20</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9655,14 +9655,14 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>TC_FILE_004</t>
+          <t>TC_FILE_001</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 4</t>
+          <t>Verify File Upload scenario 1</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9689,7 +9689,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>TC_FILE_005</t>
+          <t>TC_FILE_002</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 5</t>
+          <t>Verify File Upload scenario 2</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -9716,7 +9716,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>TC_FILE_006</t>
+          <t>TC_FILE_003</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 6</t>
+          <t>Verify File Upload scenario 3</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -9736,14 +9736,14 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>TC_FILE_007</t>
+          <t>TC_FILE_004</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 7</t>
+          <t>Verify File Upload scenario 4</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -9763,14 +9763,14 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>TC_FILE_008</t>
+          <t>TC_FILE_005</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 8</t>
+          <t>Verify File Upload scenario 5</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -9790,14 +9790,14 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TC_FILE_009</t>
+          <t>TC_FILE_006</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 9</t>
+          <t>Verify File Upload scenario 6</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -9824,7 +9824,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TC_FILE_010</t>
+          <t>TC_FILE_007</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 10</t>
+          <t>Verify File Upload scenario 7</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -9851,7 +9851,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>TC_FILE_011</t>
+          <t>TC_FILE_008</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 11</t>
+          <t>Verify File Upload scenario 8</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -9878,7 +9878,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>TC_FILE_012</t>
+          <t>TC_FILE_009</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 12</t>
+          <t>Verify File Upload scenario 9</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -9905,7 +9905,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TC_FILE_013</t>
+          <t>TC_FILE_010</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 13</t>
+          <t>Verify File Upload scenario 10</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -9932,7 +9932,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>TC_FILE_014</t>
+          <t>TC_FILE_011</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 14</t>
+          <t>Verify File Upload scenario 11</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -9959,7 +9959,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>TC_FILE_015</t>
+          <t>TC_FILE_012</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 15</t>
+          <t>Verify File Upload scenario 12</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>TC_FILE_016</t>
+          <t>TC_FILE_013</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9996,7 +9996,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 16</t>
+          <t>Verify File Upload scenario 13</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -10006,14 +10006,14 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>TC_FILE_017</t>
+          <t>TC_FILE_014</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 17</t>
+          <t>Verify File Upload scenario 14</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -10033,14 +10033,14 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>TC_FILE_018</t>
+          <t>TC_FILE_015</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 18</t>
+          <t>Verify File Upload scenario 15</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -10060,14 +10060,14 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>TC_FILE_019</t>
+          <t>TC_FILE_016</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 19</t>
+          <t>Verify File Upload scenario 16</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -10094,7 +10094,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>TC_FILE_020</t>
+          <t>TC_FILE_017</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -10104,7 +10104,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Verify File Upload scenario 20</t>
+          <t>Verify File Upload scenario 17</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -10121,17 +10121,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TC_ACC_001</t>
+          <t>TC_FILE_018</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 1</t>
+          <t>Verify File Upload scenario 18</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -10141,24 +10141,24 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>TC_ACC_002</t>
+          <t>TC_FILE_019</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 2</t>
+          <t>Verify File Upload scenario 19</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -10168,24 +10168,24 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>TC_ACC_003</t>
+          <t>TC_FILE_020</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>File Upload</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 3</t>
+          <t>Verify File Upload scenario 20</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -10195,14 +10195,14 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>TC_ACC_004</t>
+          <t>TC_ACC_001</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 4</t>
+          <t>Verify Accessibility scenario 1</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -10229,7 +10229,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>TC_ACC_005</t>
+          <t>TC_ACC_002</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 5</t>
+          <t>Verify Accessibility scenario 2</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -10256,7 +10256,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>TC_ACC_006</t>
+          <t>TC_ACC_003</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 6</t>
+          <t>Verify Accessibility scenario 3</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10276,14 +10276,14 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>TC_ACC_007</t>
+          <t>TC_ACC_004</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 7</t>
+          <t>Verify Accessibility scenario 4</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10303,14 +10303,14 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>TC_ACC_008</t>
+          <t>TC_ACC_005</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 8</t>
+          <t>Verify Accessibility scenario 5</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -10330,14 +10330,14 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>TC_ACC_009</t>
+          <t>TC_ACC_006</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 9</t>
+          <t>Verify Accessibility scenario 6</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>TC_ACC_010</t>
+          <t>TC_ACC_007</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 10</t>
+          <t>Verify Accessibility scenario 7</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10391,7 +10391,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>TC_ACC_011</t>
+          <t>TC_ACC_008</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 11</t>
+          <t>Verify Accessibility scenario 8</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10418,7 +10418,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>TC_ACC_012</t>
+          <t>TC_ACC_009</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 12</t>
+          <t>Verify Accessibility scenario 9</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10445,7 +10445,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>TC_ACC_013</t>
+          <t>TC_ACC_010</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 13</t>
+          <t>Verify Accessibility scenario 10</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10472,7 +10472,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>TC_ACC_014</t>
+          <t>TC_ACC_011</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 14</t>
+          <t>Verify Accessibility scenario 11</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10499,7 +10499,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>TC_ACC_015</t>
+          <t>TC_ACC_012</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -10509,7 +10509,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 15</t>
+          <t>Verify Accessibility scenario 12</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10526,7 +10526,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>TC_ACC_016</t>
+          <t>TC_ACC_013</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 16</t>
+          <t>Verify Accessibility scenario 13</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10546,14 +10546,14 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>TC_ACC_017</t>
+          <t>TC_ACC_014</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 17</t>
+          <t>Verify Accessibility scenario 14</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -10573,14 +10573,14 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>TC_ACC_018</t>
+          <t>TC_ACC_015</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 18</t>
+          <t>Verify Accessibility scenario 15</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10600,14 +10600,14 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>TC_ACC_019</t>
+          <t>TC_ACC_016</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 19</t>
+          <t>Verify Accessibility scenario 16</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -10634,7 +10634,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>TC_ACC_020</t>
+          <t>TC_ACC_017</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Verify Accessibility scenario 20</t>
+          <t>Verify Accessibility scenario 17</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10661,17 +10661,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>TC_RESP_001</t>
+          <t>TC_ACC_018</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Responsive Design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 1</t>
+          <t>Verify Accessibility scenario 18</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -10681,24 +10681,24 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>TC_RESP_002</t>
+          <t>TC_ACC_019</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Responsive Design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 2</t>
+          <t>Verify Accessibility scenario 19</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10708,24 +10708,24 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>TC_RESP_003</t>
+          <t>TC_ACC_020</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Responsive Design</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 3</t>
+          <t>Verify Accessibility scenario 20</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>TC_RESP_004</t>
+          <t>TC_RESP_001</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 4</t>
+          <t>Verify Responsive Design scenario 1</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>TC_RESP_005</t>
+          <t>TC_RESP_002</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 5</t>
+          <t>Verify Responsive Design scenario 2</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -10796,7 +10796,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>TC_RESP_006</t>
+          <t>TC_RESP_003</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 6</t>
+          <t>Verify Responsive Design scenario 3</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10816,14 +10816,14 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>TC_RESP_007</t>
+          <t>TC_RESP_004</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 7</t>
+          <t>Verify Responsive Design scenario 4</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10843,14 +10843,14 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>TC_RESP_008</t>
+          <t>TC_RESP_005</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 8</t>
+          <t>Verify Responsive Design scenario 5</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10870,14 +10870,14 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>TC_RESP_009</t>
+          <t>TC_RESP_006</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 9</t>
+          <t>Verify Responsive Design scenario 6</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10904,7 +10904,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>TC_RESP_010</t>
+          <t>TC_RESP_007</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 10</t>
+          <t>Verify Responsive Design scenario 7</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10931,7 +10931,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>TC_RESP_011</t>
+          <t>TC_RESP_008</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 11</t>
+          <t>Verify Responsive Design scenario 8</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>TC_RESP_012</t>
+          <t>TC_RESP_009</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 12</t>
+          <t>Verify Responsive Design scenario 9</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -10985,7 +10985,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>TC_RESP_013</t>
+          <t>TC_RESP_010</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 13</t>
+          <t>Verify Responsive Design scenario 10</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -11012,7 +11012,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>TC_RESP_014</t>
+          <t>TC_RESP_011</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 14</t>
+          <t>Verify Responsive Design scenario 11</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -11039,7 +11039,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>TC_RESP_015</t>
+          <t>TC_RESP_012</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 15</t>
+          <t>Verify Responsive Design scenario 12</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -11066,7 +11066,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>TC_RESP_016</t>
+          <t>TC_RESP_013</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 16</t>
+          <t>Verify Responsive Design scenario 13</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -11086,14 +11086,14 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>TC_RESP_017</t>
+          <t>TC_RESP_014</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 17</t>
+          <t>Verify Responsive Design scenario 14</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -11113,14 +11113,14 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>TC_RESP_018</t>
+          <t>TC_RESP_015</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 18</t>
+          <t>Verify Responsive Design scenario 15</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -11140,14 +11140,14 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>TC_RESP_019</t>
+          <t>TC_RESP_016</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 19</t>
+          <t>Verify Responsive Design scenario 16</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -11174,7 +11174,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>TC_RESP_020</t>
+          <t>TC_RESP_017</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Verify Responsive Design scenario 20</t>
+          <t>Verify Responsive Design scenario 17</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -11201,17 +11201,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>TC_PERF_001</t>
+          <t>TC_RESP_018</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 1</t>
+          <t>Verify Responsive Design scenario 18</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -11221,24 +11221,24 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>TC_PERF_002</t>
+          <t>TC_RESP_019</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 2</t>
+          <t>Verify Responsive Design scenario 19</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -11248,24 +11248,24 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>TC_PERF_003</t>
+          <t>TC_RESP_020</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Performance Smoke Tests</t>
+          <t>Responsive Design</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 3</t>
+          <t>Verify Responsive Design scenario 20</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -11275,14 +11275,14 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>TC_PERF_004</t>
+          <t>TC_PERF_001</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 4</t>
+          <t>Verify Performance Smoke Tests scenario 1</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -11309,7 +11309,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>TC_PERF_005</t>
+          <t>TC_PERF_002</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 5</t>
+          <t>Verify Performance Smoke Tests scenario 2</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -11336,7 +11336,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>TC_PERF_006</t>
+          <t>TC_PERF_003</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 6</t>
+          <t>Verify Performance Smoke Tests scenario 3</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -11356,14 +11356,14 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>TC_PERF_007</t>
+          <t>TC_PERF_004</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -11373,7 +11373,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 7</t>
+          <t>Verify Performance Smoke Tests scenario 4</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>TC_PERF_008</t>
+          <t>TC_PERF_005</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 8</t>
+          <t>Verify Performance Smoke Tests scenario 5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -11410,14 +11410,14 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>TC_PERF_009</t>
+          <t>TC_PERF_006</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 9</t>
+          <t>Verify Performance Smoke Tests scenario 6</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -11444,7 +11444,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>TC_PERF_010</t>
+          <t>TC_PERF_007</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -11454,7 +11454,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 10</t>
+          <t>Verify Performance Smoke Tests scenario 7</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -11471,7 +11471,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>TC_PERF_011</t>
+          <t>TC_PERF_008</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 11</t>
+          <t>Verify Performance Smoke Tests scenario 8</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>TC_PERF_012</t>
+          <t>TC_PERF_009</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 12</t>
+          <t>Verify Performance Smoke Tests scenario 9</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -11525,7 +11525,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>TC_PERF_013</t>
+          <t>TC_PERF_010</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 13</t>
+          <t>Verify Performance Smoke Tests scenario 10</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -11552,7 +11552,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>TC_PERF_014</t>
+          <t>TC_PERF_011</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 14</t>
+          <t>Verify Performance Smoke Tests scenario 11</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -11579,7 +11579,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>TC_PERF_015</t>
+          <t>TC_PERF_012</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 15</t>
+          <t>Verify Performance Smoke Tests scenario 12</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11606,7 +11606,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>TC_PERF_016</t>
+          <t>TC_PERF_013</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 16</t>
+          <t>Verify Performance Smoke Tests scenario 13</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11626,14 +11626,14 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TC_PERF_017</t>
+          <t>TC_PERF_014</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 17</t>
+          <t>Verify Performance Smoke Tests scenario 14</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -11653,14 +11653,14 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>TC_PERF_018</t>
+          <t>TC_PERF_015</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 18</t>
+          <t>Verify Performance Smoke Tests scenario 15</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11680,14 +11680,14 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>TC_PERF_019</t>
+          <t>TC_PERF_016</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 19</t>
+          <t>Verify Performance Smoke Tests scenario 16</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -11714,7 +11714,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>TC_PERF_020</t>
+          <t>TC_PERF_017</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Verify Performance Smoke Tests scenario 20</t>
+          <t>Verify Performance Smoke Tests scenario 17</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -11741,17 +11741,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>TC_REGR_001</t>
+          <t>TC_PERF_018</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 1</t>
+          <t>Verify Performance Smoke Tests scenario 18</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -11761,24 +11761,24 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>TC_REGR_002</t>
+          <t>TC_PERF_019</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 2</t>
+          <t>Verify Performance Smoke Tests scenario 19</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
@@ -11788,24 +11788,24 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>TC_REGR_003</t>
+          <t>TC_PERF_020</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Regression Suite</t>
+          <t>Performance Smoke Tests</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 3</t>
+          <t>Verify Performance Smoke Tests scenario 20</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -11815,14 +11815,14 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>TC_REGR_004</t>
+          <t>TC_REGR_001</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 4</t>
+          <t>Verify Regression Suite scenario 1</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -11849,7 +11849,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>TC_REGR_005</t>
+          <t>TC_REGR_002</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 5</t>
+          <t>Verify Regression Suite scenario 2</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>TC_REGR_006</t>
+          <t>TC_REGR_003</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 6</t>
+          <t>Verify Regression Suite scenario 3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -11896,14 +11896,14 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>TC_REGR_007</t>
+          <t>TC_REGR_004</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 7</t>
+          <t>Verify Regression Suite scenario 4</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -11923,14 +11923,14 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>TC_REGR_008</t>
+          <t>TC_REGR_005</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 8</t>
+          <t>Verify Regression Suite scenario 5</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -11950,14 +11950,14 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>TC_REGR_009</t>
+          <t>TC_REGR_006</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 9</t>
+          <t>Verify Regression Suite scenario 6</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11984,7 +11984,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TC_REGR_010</t>
+          <t>TC_REGR_007</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 10</t>
+          <t>Verify Regression Suite scenario 7</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -12011,7 +12011,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>TC_REGR_011</t>
+          <t>TC_REGR_008</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 11</t>
+          <t>Verify Regression Suite scenario 8</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -12038,7 +12038,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>TC_REGR_012</t>
+          <t>TC_REGR_009</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 12</t>
+          <t>Verify Regression Suite scenario 9</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>TC_REGR_013</t>
+          <t>TC_REGR_010</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -12075,7 +12075,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 13</t>
+          <t>Verify Regression Suite scenario 10</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -12092,7 +12092,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>TC_REGR_014</t>
+          <t>TC_REGR_011</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -12102,7 +12102,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 14</t>
+          <t>Verify Regression Suite scenario 11</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -12119,7 +12119,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>TC_REGR_015</t>
+          <t>TC_REGR_012</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 15</t>
+          <t>Verify Regression Suite scenario 12</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -12146,7 +12146,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>TC_REGR_016</t>
+          <t>TC_REGR_013</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 16</t>
+          <t>Verify Regression Suite scenario 13</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -12166,14 +12166,14 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>TC_REGR_017</t>
+          <t>TC_REGR_014</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 17</t>
+          <t>Verify Regression Suite scenario 14</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12193,14 +12193,14 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>TC_REGR_018</t>
+          <t>TC_REGR_015</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -12210,7 +12210,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 18</t>
+          <t>Verify Regression Suite scenario 15</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -12220,14 +12220,14 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>TC_REGR_019</t>
+          <t>TC_REGR_016</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 19</t>
+          <t>Verify Regression Suite scenario 16</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>TC_REGR_020</t>
+          <t>TC_REGR_017</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 20</t>
+          <t>Verify Regression Suite scenario 17</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -12281,7 +12281,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>TC_REGR_021</t>
+          <t>TC_REGR_018</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 21</t>
+          <t>Verify Regression Suite scenario 18</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12308,7 +12308,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>TC_REGR_022</t>
+          <t>TC_REGR_019</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 22</t>
+          <t>Verify Regression Suite scenario 19</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TC_REGR_023</t>
+          <t>TC_REGR_020</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 23</t>
+          <t>Verify Regression Suite scenario 20</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -12362,7 +12362,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>TC_REGR_024</t>
+          <t>TC_REGR_021</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 24</t>
+          <t>Verify Regression Suite scenario 21</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -12389,7 +12389,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TC_REGR_025</t>
+          <t>TC_REGR_022</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 25</t>
+          <t>Verify Regression Suite scenario 22</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -12416,7 +12416,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>TC_REGR_026</t>
+          <t>TC_REGR_023</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 26</t>
+          <t>Verify Regression Suite scenario 23</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -12443,7 +12443,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TC_REGR_027</t>
+          <t>TC_REGR_024</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 27</t>
+          <t>Verify Regression Suite scenario 24</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -12470,7 +12470,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>TC_REGR_028</t>
+          <t>TC_REGR_025</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 28</t>
+          <t>Verify Regression Suite scenario 25</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -12497,7 +12497,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>TC_REGR_029</t>
+          <t>TC_REGR_026</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 29</t>
+          <t>Verify Regression Suite scenario 26</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TC_REGR_030</t>
+          <t>TC_REGR_027</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 30</t>
+          <t>Verify Regression Suite scenario 27</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -12551,7 +12551,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>TC_REGR_031</t>
+          <t>TC_REGR_028</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 31</t>
+          <t>Verify Regression Suite scenario 28</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -12578,7 +12578,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>TC_REGR_032</t>
+          <t>TC_REGR_029</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 32</t>
+          <t>Verify Regression Suite scenario 29</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -12605,7 +12605,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>TC_REGR_033</t>
+          <t>TC_REGR_030</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 33</t>
+          <t>Verify Regression Suite scenario 30</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>TC_REGR_034</t>
+          <t>TC_REGR_031</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 34</t>
+          <t>Verify Regression Suite scenario 31</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -12659,7 +12659,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>TC_REGR_035</t>
+          <t>TC_REGR_032</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 35</t>
+          <t>Verify Regression Suite scenario 32</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -12686,7 +12686,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>TC_REGR_036</t>
+          <t>TC_REGR_033</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 36</t>
+          <t>Verify Regression Suite scenario 33</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12713,7 +12713,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TC_REGR_037</t>
+          <t>TC_REGR_034</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 37</t>
+          <t>Verify Regression Suite scenario 34</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -12740,7 +12740,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>TC_REGR_038</t>
+          <t>TC_REGR_035</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 38</t>
+          <t>Verify Regression Suite scenario 35</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -12767,7 +12767,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>TC_REGR_039</t>
+          <t>TC_REGR_036</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -12777,7 +12777,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 39</t>
+          <t>Verify Regression Suite scenario 36</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -12794,7 +12794,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>TC_REGR_040</t>
+          <t>TC_REGR_037</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 40</t>
+          <t>Verify Regression Suite scenario 37</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -12821,7 +12821,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TC_REGR_041</t>
+          <t>TC_REGR_038</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -12831,7 +12831,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 41</t>
+          <t>Verify Regression Suite scenario 38</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12848,7 +12848,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>TC_REGR_042</t>
+          <t>TC_REGR_039</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 42</t>
+          <t>Verify Regression Suite scenario 39</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -12875,7 +12875,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>TC_REGR_043</t>
+          <t>TC_REGR_040</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 43</t>
+          <t>Verify Regression Suite scenario 40</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -12902,7 +12902,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>TC_REGR_044</t>
+          <t>TC_REGR_041</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 44</t>
+          <t>Verify Regression Suite scenario 41</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -12929,7 +12929,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>TC_REGR_045</t>
+          <t>TC_REGR_042</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 45</t>
+          <t>Verify Regression Suite scenario 42</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -12956,7 +12956,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>TC_REGR_046</t>
+          <t>TC_REGR_043</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 46</t>
+          <t>Verify Regression Suite scenario 43</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -12983,7 +12983,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>TC_REGR_047</t>
+          <t>TC_REGR_044</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 47</t>
+          <t>Verify Regression Suite scenario 44</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>TC_REGR_048</t>
+          <t>TC_REGR_045</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 48</t>
+          <t>Verify Regression Suite scenario 45</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -13037,7 +13037,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TC_REGR_049</t>
+          <t>TC_REGR_046</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Verify Regression Suite scenario 49</t>
+          <t>Verify Regression Suite scenario 46</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -13064,25 +13064,106 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
+          <t>TC_REGR_047</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Verify Regression Suite scenario 47</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>TC_REGR_048</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Verify Regression Suite scenario 48</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>TC_REGR_049</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Regression Suite</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Verify Regression Suite scenario 49</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
           <t>TC_REGR_050</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>Regression Suite</t>
         </is>
       </c>
-      <c r="C468" t="inlineStr">
+      <c r="C471" t="inlineStr">
         <is>
           <t>Verify Regression Suite scenario 50</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>Passed</t>
-        </is>
-      </c>
-      <c r="E468" t="inlineStr">
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
